--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T09:23:28+00:00</t>
+    <t>2026-07-17T06:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -645,6 +645,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Procedure.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
   </si>
   <si>
     <t>Procedure.modifierExtension</t>
@@ -1869,12 +1885,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN68"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.2890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -4080,43 +4096,41 @@
         <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4164,7 +4178,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4173,7 +4187,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -4182,7 +4196,7 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>21</v>
@@ -4200,38 +4214,38 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4280,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4292,27 +4306,27 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4335,16 +4349,20 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4392,7 +4410,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4407,24 +4425,24 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4447,7 +4465,7 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>224</v>
@@ -4455,9 +4473,7 @@
       <c r="M23" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>226</v>
-      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4506,7 +4522,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4521,10 +4537,10 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4542,7 +4558,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4561,15 +4577,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4633,10 +4651,10 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
@@ -4647,14 +4665,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4673,17 +4691,15 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L25" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>240</v>
-      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4732,7 +4748,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4747,10 +4763,10 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4759,44 +4775,44 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4822,11 +4838,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4844,13 +4862,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4859,56 +4877,56 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4934,13 +4952,11 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4958,10 +4974,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>87</v>
@@ -4973,13 +4989,13 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
@@ -4987,21 +5003,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -5013,15 +5029,17 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5049,10 +5067,10 @@
         <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5070,7 +5088,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5085,38 +5103,38 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5125,18 +5143,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -5160,11 +5176,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5182,7 +5200,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5197,56 +5215,58 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>277</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>103</v>
+        <v>276</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5270,13 +5290,11 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5294,7 +5312,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>104</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5306,38 +5324,38 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>105</v>
+        <v>280</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>21</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5349,17 +5367,15 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5396,31 +5412,31 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -5437,14 +5453,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5460,23 +5476,21 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>109</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5512,19 +5526,19 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>285</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5536,27 +5550,27 @@
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>286</v>
+        <v>105</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5567,7 +5581,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -5579,19 +5593,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="O33" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5640,13 +5654,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5658,35 +5672,35 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
@@ -5695,16 +5709,20 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
       </c>
@@ -5752,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>87</v>
@@ -5767,38 +5785,38 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5807,17 +5825,15 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5866,10 +5882,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>87</v>
@@ -5881,24 +5897,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5909,7 +5925,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5921,16 +5937,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5980,7 +5996,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5995,24 +6011,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6020,13 +6036,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -6035,15 +6051,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6092,7 +6110,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6107,24 +6125,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM37" t="s" s="2">
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" hidden="true">
-      <c r="A38" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="B38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6132,13 +6150,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6147,13 +6165,13 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6204,7 +6222,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6222,10 +6240,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6233,10 +6251,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6247,7 +6265,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6259,13 +6277,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6316,13 +6334,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6331,13 +6349,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6345,10 +6363,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6359,7 +6377,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6368,16 +6386,16 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>101</v>
+        <v>341</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>102</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>103</v>
+        <v>343</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6428,25 +6446,25 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>104</v>
+        <v>340</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>105</v>
+        <v>345</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6457,21 +6475,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6483,17 +6501,15 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6542,19 +6558,19 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
@@ -6571,14 +6587,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>344</v>
+        <v>107</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6591,26 +6607,24 @@
         <v>21</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>346</v>
+        <v>110</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O42" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6658,7 +6672,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>347</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6676,7 +6690,7 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6694,36 +6708,38 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>351</v>
+        <v>210</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6748,63 +6764,63 @@
         <v>21</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>354</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>355</v>
+        <v>191</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6812,7 +6828,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
@@ -6827,17 +6843,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6862,13 +6878,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6886,10 +6902,10 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>87</v>
@@ -6901,24 +6917,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6926,7 +6942,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>87</v>
@@ -6938,20 +6954,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7000,10 +7016,10 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>87</v>
@@ -7015,24 +7031,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7043,7 +7059,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7052,20 +7068,20 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7114,7 +7130,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7132,10 +7148,10 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7143,10 +7159,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7169,18 +7185,18 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>253</v>
+        <v>378</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7204,13 +7220,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7228,13 +7244,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7243,13 +7259,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7257,10 +7273,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7283,16 +7299,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>389</v>
+        <v>258</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7318,13 +7334,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7342,7 +7358,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7357,13 +7373,13 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7371,10 +7387,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7397,7 +7413,7 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>253</v>
+        <v>394</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>395</v>
@@ -7432,13 +7448,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7456,7 +7472,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7471,24 +7487,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7511,16 +7527,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7549,10 +7565,10 @@
         <v>153</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7570,13 +7586,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7588,21 +7604,21 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>21</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7613,7 +7629,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7622,19 +7638,19 @@
         <v>21</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7660,13 +7676,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7684,13 +7700,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -7702,7 +7718,7 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
@@ -7713,10 +7729,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7727,7 +7743,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7739,7 +7755,7 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>415</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>416</v>
@@ -7774,13 +7790,13 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -7798,7 +7814,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7816,7 +7832,7 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
@@ -7827,10 +7843,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7853,18 +7869,18 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>426</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -7888,13 +7904,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7912,7 +7928,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7930,7 +7946,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7967,16 +7983,18 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>253</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8000,13 +8018,13 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -8042,7 +8060,7 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -8053,10 +8071,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8067,7 +8085,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8079,13 +8097,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8112,13 +8130,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>21</v>
+        <v>435</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8136,7 +8154,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8151,24 +8169,24 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8191,13 +8209,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>439</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>102</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>103</v>
+        <v>441</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8248,50 +8266,50 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>104</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>442</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>105</v>
+        <v>443</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>21</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8303,17 +8321,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8350,31 +8366,31 @@
         <v>21</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8391,21 +8407,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8414,19 +8430,19 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>443</v>
+        <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>444</v>
+        <v>109</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>445</v>
+        <v>110</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>446</v>
+        <v>111</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8464,51 +8480,51 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>115</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>448</v>
+        <v>105</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8531,15 +8547,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>315</v>
+        <v>448</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8628,10 +8646,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>21</v>
@@ -8643,13 +8661,13 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8700,10 +8718,10 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>87</v>
@@ -8718,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
@@ -8729,10 +8747,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8740,10 +8758,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -8752,10 +8770,10 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>336</v>
+        <v>460</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>461</v>
@@ -8812,13 +8830,13 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>21</v>
@@ -8830,21 +8848,21 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8855,7 +8873,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -8867,13 +8885,13 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>101</v>
+        <v>341</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>102</v>
+        <v>466</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>103</v>
+        <v>467</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8924,25 +8942,25 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>104</v>
+        <v>465</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>105</v>
+        <v>468</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -8953,21 +8971,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -8979,17 +8997,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9038,19 +9054,19 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
@@ -9067,14 +9083,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>344</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9087,26 +9103,24 @@
         <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>345</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>346</v>
+        <v>110</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
       </c>
@@ -9154,7 +9168,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>347</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9172,7 +9186,7 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>21</v>
@@ -9183,42 +9197,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>350</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9242,13 +9260,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -9266,25 +9284,25 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>352</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>472</v>
+        <v>191</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
@@ -9295,10 +9313,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9306,7 +9324,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>87</v>
@@ -9321,13 +9339,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9354,13 +9372,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9378,10 +9396,10 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>87</v>
@@ -9418,10 +9436,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9441,12 +9459,8 @@
       <c r="M67" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>483</v>
-      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9497,10 +9511,10 @@
         <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
@@ -9512,7 +9526,7 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>21</v>
@@ -9523,10 +9537,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9549,18 +9563,20 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>253</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="N68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9584,13 +9600,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>489</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -9608,7 +9624,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9626,17 +9642,131 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN68" t="s" s="2">
+      <c r="B69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN68">
+  <autoFilter ref="A1:AN69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9646,7 +9776,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4337,7 +4337,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1390,7 +1390,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zur Prozedur für Zusatzinformation</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:02:16+00:00</t>
+    <t>2026-08-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2186" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:50:30+00:00</t>
+    <t>2026-08-28T05:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,7 +323,421 @@
 </t>
   </si>
   <si>
-    <t>Procedure.meta.id</t>
+    <t>Procedure.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Procedure.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Procedure.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Procedure.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Procedure.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Procedure.extension:reported</t>
+  </si>
+  <si>
+    <t>reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Reported (Fremdangabe)</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Procedure.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
+  </si>
+  <si>
+    <t>Procedure.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=DEFN].target</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Verweis auf ein externes Dokument</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Event.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis auf eine Anforderung</t>
+  </si>
+  <si>
+    <t>A reference to a resource that contains details of the request for this procedure.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target[classCode=(various e.g. PROC, OBS, PCPR, ACT,  moodCode=RQO].code</t>
+  </si>
+  <si>
+    <t>Procedure.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular procedure is a component or step.</t>
+  </si>
+  <si>
+    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=SBADM or PROC or OBS, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Procedure.status</t>
+  </si>
+  <si>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
+  </si>
+  <si>
+    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
+This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Procedure.statusReason</t>
+  </si>
+  <si>
+    <t>Suspended Reason
+Cancelled Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+  </si>
+  <si>
+    <t>Captures the reason for the current state of the procedure.</t>
+  </si>
+  <si>
+    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>A code that identifies the reason a procedure was not performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Event.statusReason</t>
+  </si>
+  <si>
+    <t>.reason.Observation.value</t>
+  </si>
+  <si>
+    <t>Procedure.category</t>
+  </si>
+  <si>
+    <t>Kategorisierung nach Verfahren</t>
+  </si>
+  <si>
+    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-category|4.0.1</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Procedure.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type
+</t>
+  </si>
+  <si>
+    <t>Prozedurencode der durchgeführten Prozedur</t>
+  </si>
+  <si>
+    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
+  </si>
+  <si>
+    <t>0..1 to account for primarily narrative only resources.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>OBR-44/OBR-45</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -342,15 +756,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Procedure.meta.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
+    <t>Procedure.code.extension</t>
   </si>
   <si>
     <t>Additional content defined by implementations</t>
@@ -359,556 +765,17 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Procedure.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Procedure.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Procedure.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Procedure.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Procedure.meta.security</t>
+    <t>Procedure.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>Procedure.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Procedure.meta.tag:diagnosisType</t>
-  </si>
-  <si>
-    <t>diagnosisType</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-type</t>
-  </si>
-  <si>
-    <t>Procedure.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Procedure.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Procedure.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Procedure.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Procedure.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension:reported</t>
-  </si>
-  <si>
-    <t>reported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Reported (Fremdangabe)</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Procedure.extension:entered-in-error</t>
-  </si>
-  <si>
-    <t>entered-in-error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Entered In Error</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
-  </si>
-  <si>
-    <t>Procedure.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Some combination of ORC-2 / ORC-3 / OBR-2 / OBR-3 / IPC-1 / IPC-2 / IPC-3 / IPC-4</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=DEFN].target</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Verweis auf ein externes Dokument</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Event.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Procedure.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis auf eine Anforderung</t>
-  </si>
-  <si>
-    <t>A reference to a resource that contains details of the request for this procedure.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target[classCode=(various e.g. PROC, OBS, PCPR, ACT,  moodCode=RQO].code</t>
-  </si>
-  <si>
-    <t>Procedure.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular procedure is a component or step.</t>
-  </si>
-  <si>
-    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=SBADM or PROC or OBS, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Procedure.status</t>
-  </si>
-  <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
-  </si>
-  <si>
-    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
-This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Procedure.statusReason</t>
-  </si>
-  <si>
-    <t>Suspended Reason
-Cancelled Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the procedure.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>A code that identifies the reason a procedure was not performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Event.statusReason</t>
-  </si>
-  <si>
-    <t>.reason.Observation.value</t>
-  </si>
-  <si>
-    <t>Procedure.category</t>
-  </si>
-  <si>
-    <t>Kategorisierung nach Verfahren</t>
-  </si>
-  <si>
-    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Procedure.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type
-</t>
-  </si>
-  <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
-  </si>
-  <si>
-    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
-  </si>
-  <si>
-    <t>0..1 to account for primarily narrative only resources.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>OBR-44/OBR-45</t>
-  </si>
-  <si>
-    <t>Procedure.code.id</t>
-  </si>
-  <si>
-    <t>Procedure.code.extension</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1885,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.2890625" customWidth="true" bestFit="true"/>
@@ -1912,7 +1779,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="54.46484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2411,10 +2278,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>101</v>
@@ -2425,7 +2292,9 @@
       <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2474,7 +2343,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2486,13 +2355,13 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>21</v>
@@ -2510,14 +2379,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2529,16 +2398,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2564,49 +2433,49 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>21</v>
@@ -2617,14 +2486,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2640,10 +2509,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>118</v>
@@ -2720,7 +2589,7 @@
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>21</v>
@@ -2731,21 +2600,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2754,19 +2623,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2816,25 +2685,25 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>21</v>
@@ -2845,10 +2714,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2859,7 +2728,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2868,20 +2737,18 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2918,31 +2785,29 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -2959,12 +2824,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2973,7 +2840,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2982,20 +2849,18 @@
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3044,7 +2909,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3053,10 +2918,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3073,12 +2938,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3087,7 +2954,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3096,20 +2963,18 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -3134,13 +2999,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -3158,7 +3023,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3167,10 +3032,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3187,18 +3052,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -3207,24 +3072,26 @@
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3248,29 +3115,31 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AC12" s="2"/>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3282,13 +3151,13 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>21</v>
@@ -3299,23 +3168,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3327,18 +3194,20 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3362,11 +3231,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3399,24 +3270,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3427,29 +3298,27 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3498,13 +3367,13 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
@@ -3513,10 +3382,10 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
@@ -3527,10 +3396,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3541,7 +3410,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -3550,19 +3419,19 @@
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3588,37 +3457,37 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -3627,10 +3496,10 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3641,21 +3510,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3664,20 +3533,18 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3726,13 +3593,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -3741,10 +3608,10 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3755,21 +3622,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3778,19 +3645,19 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3840,7 +3707,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3852,13 +3719,13 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3867,12 +3734,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3880,30 +3747,32 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3928,50 +3797,50 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>21</v>
@@ -3979,16 +3848,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4004,18 +3871,20 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4040,13 +3909,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4064,25 +3933,25 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>21</v>
@@ -4093,14 +3962,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>21</v>
       </c>
@@ -4109,7 +3976,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -4118,16 +3985,16 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4154,13 +4021,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4178,74 +4045,72 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>221</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4270,13 +4135,11 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4294,39 +4157,39 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>21</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4337,7 +4200,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4346,23 +4209,19 @@
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4410,50 +4269,50 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>21</v>
@@ -4462,18 +4321,20 @@
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4510,19 +4371,19 @@
         <v>21</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4534,13 +4395,13 @@
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
@@ -4551,10 +4412,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4565,7 +4426,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>21</v>
@@ -4577,18 +4438,20 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -4636,7 +4499,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4651,28 +4514,28 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4691,16 +4554,20 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -4748,13 +4615,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4763,38 +4630,38 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -4803,17 +4670,15 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4862,13 +4727,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4877,24 +4742,24 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>21</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4902,31 +4767,31 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4952,11 +4817,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4974,10 +4841,10 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>87</v>
@@ -4989,28 +4856,28 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5029,16 +4896,16 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5064,13 +4931,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>263</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5088,7 +4955,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5103,24 +4970,24 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5128,13 +4995,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5143,13 +5010,13 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>258</v>
+        <v>286</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5176,13 +5043,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5200,7 +5067,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5218,35 +5085,35 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5255,18 +5122,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5290,11 +5155,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5312,7 +5179,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5327,24 +5194,24 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5355,7 +5222,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5364,16 +5231,16 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>298</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>103</v>
+        <v>300</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5424,25 +5291,25 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>104</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>105</v>
+        <v>302</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
@@ -5453,21 +5320,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -5479,17 +5346,15 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5526,37 +5391,37 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>115</v>
+        <v>234</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
@@ -5567,14 +5432,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5590,23 +5455,21 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>286</v>
+        <v>237</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>287</v>
+        <v>238</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -5654,7 +5517,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5666,62 +5529,62 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>291</v>
+        <v>235</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>296</v>
+        <v>154</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>297</v>
+        <v>155</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5770,53 +5633,53 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>299</v>
+        <v>130</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5825,16 +5688,18 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>303</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -5858,13 +5723,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>21</v>
+        <v>314</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>21</v>
+        <v>315</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -5882,10 +5747,10 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>87</v>
@@ -5897,24 +5762,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>308</v>
+        <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5922,10 +5787,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5937,18 +5802,18 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5996,10 +5861,10 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>87</v>
@@ -6011,24 +5876,24 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6048,21 +5913,21 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6110,7 +5975,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6125,24 +5990,24 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>326</v>
+        <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6150,13 +6015,13 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6165,16 +6030,18 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -6222,7 +6089,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6240,10 +6107,10 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6251,10 +6118,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6265,7 +6132,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6277,15 +6144,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>204</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6310,13 +6179,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6334,13 +6203,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6349,13 +6218,13 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6363,10 +6232,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6389,15 +6258,17 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6446,7 +6317,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6461,13 +6332,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6475,10 +6346,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6489,7 +6360,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6498,18 +6369,20 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>102</v>
+        <v>357</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6534,13 +6407,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>360</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6558,50 +6431,50 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6610,19 +6483,19 @@
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>109</v>
+        <v>365</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6648,13 +6521,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6672,25 +6545,25 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>115</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>105</v>
+        <v>370</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6701,14 +6574,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6721,26 +6594,24 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>372</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6788,7 +6659,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6800,13 +6671,13 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>191</v>
+        <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6817,10 +6688,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6831,7 +6702,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
@@ -6840,21 +6711,21 @@
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6878,13 +6749,13 @@
         <v>21</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>21</v>
@@ -6902,13 +6773,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -6917,24 +6788,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>361</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6942,10 +6813,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -6954,20 +6825,20 @@
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7016,13 +6887,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7031,24 +6902,24 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7059,7 +6930,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -7071,18 +6942,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>372</v>
+        <v>204</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7106,13 +6975,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>393</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7130,13 +6999,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7148,7 +7017,7 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
@@ -7159,10 +7028,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7173,7 +7042,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7182,21 +7051,19 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>381</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7244,13 +7111,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7259,24 +7126,24 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7287,7 +7154,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7296,20 +7163,18 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>232</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7334,13 +7199,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>388</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -7358,28 +7223,28 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>234</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>391</v>
+        <v>235</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7387,21 +7252,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7410,19 +7275,19 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>394</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>395</v>
+        <v>237</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>396</v>
+        <v>238</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>397</v>
+        <v>154</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7460,19 +7325,19 @@
         <v>21</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>240</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7484,16 +7349,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>391</v>
+        <v>235</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7501,10 +7366,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7527,16 +7392,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>258</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7562,13 +7427,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>403</v>
+        <v>21</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>404</v>
+        <v>21</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -7586,13 +7451,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7604,21 +7469,21 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>406</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7641,17 +7506,15 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>410</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7676,13 +7539,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7700,7 +7563,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7718,21 +7581,21 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7740,10 +7603,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7752,20 +7615,18 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7814,13 +7675,13 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
@@ -7832,21 +7693,21 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7869,17 +7730,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7904,13 +7763,13 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>425</v>
+        <v>21</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7928,7 +7787,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7946,7 +7805,7 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>21</v>
@@ -7957,10 +7816,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7971,7 +7830,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7983,18 +7842,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>428</v>
+        <v>231</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>232</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>233</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8042,25 +7899,25 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>427</v>
+        <v>234</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>426</v>
+        <v>235</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>21</v>
@@ -8071,21 +7928,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8097,15 +7954,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>237</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8130,13 +7989,13 @@
         <v>21</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>435</v>
+        <v>21</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>436</v>
+        <v>21</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>21</v>
@@ -8154,7 +8013,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>240</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8166,13 +8025,13 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>437</v>
+        <v>235</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>21</v>
@@ -8183,42 +8042,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>21</v>
+        <v>306</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>439</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8266,7 +8129,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>309</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8278,27 +8141,27 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>443</v>
+        <v>130</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>444</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8321,13 +8184,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>102</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>103</v>
+        <v>431</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8354,13 +8217,13 @@
         <v>21</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>21</v>
+        <v>433</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>21</v>
@@ -8378,7 +8241,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8390,13 +8253,13 @@
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>105</v>
+        <v>434</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>21</v>
@@ -8407,21 +8270,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8433,17 +8296,15 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>109</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8480,37 +8341,37 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>115</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>105</v>
+        <v>439</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>21</v>
@@ -8521,10 +8382,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8544,21 +8405,23 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -8606,13 +8469,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -8624,21 +8487,21 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8658,18 +8521,20 @@
         <v>21</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>320</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8694,13 +8559,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>451</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -8718,13 +8583,13 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>21</v>
@@ -8736,1037 +8601,17 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
-      <c r="P67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O69" s="2"/>
-      <c r="P69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN69">
+  <autoFilter ref="A1:AN60">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9776,7 +8621,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -830,7 +830,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -911,7 +911,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1765,7 +1765,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="198.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
@@ -607,7 +607,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -915,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
+    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -953,7 +953,7 @@
 </t>
   </si>
   <si>
-    <t>Diese Person hat die Prozedur durchgeführt</t>
+    <t>Person, die die Prozedur durchgeführt hat</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -1087,7 +1087,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -1118,7 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie Condition, Observation,...</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -1198,7 +1198,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation/en während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -1223,7 +1223,7 @@
 </t>
   </si>
   <si>
-    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -1257,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Prozedur für Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -1337,7 +1337,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Prozedurendurchführendes Gerät</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -1396,7 +1396,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -1415,7 +1415,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
+    <t>Code der während der Prozedur verwendeten Materialien</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,7 +515,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
@@ -546,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll.</t>
   </si>
   <si>
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -561,7 +561,7 @@
     <t>Procedure.instantiatesUri</t>
   </si>
   <si>
-    <t>Verweis auf ein externes Dokument</t>
+    <t>Verweis auf ein externes Dokument.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -584,7 +584,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine Anforderung</t>
+    <t>Verweis auf eine Anforderung.</t>
   </si>
   <si>
     <t>A reference to a resource that contains details of the request for this procedure.</t>
@@ -607,7 +607,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource.</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -625,7 +625,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -661,7 +661,7 @@
 </t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -688,7 +688,7 @@
     <t>Procedure.category</t>
   </si>
   <si>
-    <t>Kategorisierung nach Verfahren</t>
+    <t>Kategorisierung nach Verfahren.</t>
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
@@ -713,7 +713,7 @@
 </t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
+    <t>Prozedurencode der durchgeführten Prozedur.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -834,7 +834,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Prozedur bezieht</t>
+    <t>Person, auf die sich die Prozedur bezieht.</t>
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
@@ -859,7 +859,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
@@ -887,7 +887,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Durchführung</t>
+    <t>Zeitpunkt der Durchführung.</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
@@ -915,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat</t>
+    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -934,7 +934,7 @@
 </t>
   </si>
   <si>
-    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the procedure statement.</t>
@@ -953,7 +953,7 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Prozedur durchgeführt hat</t>
+    <t>Person, die die Prozedur durchgeführt hat.</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -1069,7 +1069,7 @@
 </t>
   </si>
   <si>
-    <t>Durchführungsort</t>
+    <t>Durchführungsort.</t>
   </si>
   <si>
     <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
@@ -1087,7 +1087,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code des medizinischen Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur.</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -1118,7 +1118,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie z.B. Condition oder Observation.</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -1134,7 +1134,7 @@
     <t>Procedure.bodySite</t>
   </si>
   <si>
-    <t>Betroffene Körperstelle</t>
+    <t>Betroffene Körperstelle.</t>
   </si>
   <si>
     <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
@@ -1158,7 +1158,7 @@
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>Ergebnis der Prozedur</t>
+    <t>Ergebnis der Prozedur.</t>
   </si>
   <si>
     <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
@@ -1183,7 +1183,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>This could be a histology result, pathology report, surgical report, etc.</t>
@@ -1198,7 +1198,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -1223,7 +1223,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -1235,7 +1235,7 @@
     <t>Procedure.followUp</t>
   </si>
   <si>
-    <t>Nachkontrolle (Code)</t>
+    <t>Nachkontrolle (Code).</t>
   </si>
   <si>
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
@@ -1257,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>Freitext zur Prozedur als Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation.</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -1337,7 +1337,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde.</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -1396,7 +1396,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente.</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -1415,7 +1415,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der während der Prozedur verwendeten Materialien</t>
+    <t>Code der während der Prozedur verwendeten Materialien.</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
+    <t>GDA, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-procedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
